--- a/tabtools/demo/demo_stratetab.xlsx
+++ b/tabtools/demo/demo_stratetab.xlsx
@@ -7,13 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Rates" sheetId="1" r:id="rId2"/>
+    <sheet name="Rates Formatted" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="91" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="163" uniqueCount="48">
   <si>
     <t>Table 12. Incidence Rates per 1,000 Person-Years by Sex</t>
   </si>
@@ -130,6 +131,33 @@
   </si>
   <si>
     <t>IRR = incidence rate ratio, Female vs Male. CI by log-normal method.</t>
+  </si>
+  <si>
+    <t>Table 12b. Incidence Rates, Two Decimals and 'to' Intervals</t>
+  </si>
+  <si>
+    <t>6.33 (5.45 to 7.34)</t>
+  </si>
+  <si>
+    <t>7.22 (6.16 to 8.44)</t>
+  </si>
+  <si>
+    <t>5.50 (4.62 to 6.52)</t>
+  </si>
+  <si>
+    <t>6.56 (5.49 to 7.81)</t>
+  </si>
+  <si>
+    <t>1.85 (1.39 to 2.43)</t>
+  </si>
+  <si>
+    <t>2.60 (1.99 to 3.37)</t>
+  </si>
+  <si>
+    <t>1.44 (1.00 to 2.00)</t>
+  </si>
+  <si>
+    <t>1.84 (1.29 to 2.56)</t>
   </si>
 </sst>
 </file>
@@ -248,11 +276,77 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="general" vertical="bottom" wrapText="0"/>
@@ -269,12 +363,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="general" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" wrapText="0"/>
     </xf>
@@ -285,18 +373,6 @@
       <alignment horizontal="center" vertical="bottom" wrapText="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" wrapText="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -654,4 +730,263 @@
     <mergeCell ref="B10:J10"/>
   </mergeCells>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
+    <col min="2" max="2" width="18.7109375" style="1" customWidth="true"/>
+    <col min="3" max="3" width="8.7109375" style="1" customWidth="true"/>
+    <col min="4" max="4" width="19.7109375" style="1" customWidth="true"/>
+    <col min="5" max="5" width="23.7109375" style="1" customWidth="true"/>
+    <col min="6" max="6" width="8.7109375" style="1" customWidth="true"/>
+    <col min="7" max="7" width="19.7109375" style="1" customWidth="true"/>
+    <col min="8" max="8" width="23.7109375" style="1" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="39" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="29" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="31" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B2:B3"/>
+  </mergeCells>
+</worksheet>
 </file>